--- a/data/export/2026-09-15-182路.xlsx
+++ b/data/export/2026-09-15-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC71"/>
+  <dimension ref="A1:AC95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,22 +1299,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,22 +1418,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,22 +1656,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,22 +1775,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,22 +1894,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,22 +2013,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,17 +2132,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,22 +2251,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2370,22 +2370,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2489,22 +2489,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2608,17 +2608,17 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2727,22 +2727,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2846,17 +2846,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2965,22 +2965,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3213,12 +3213,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3322,22 +3322,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3441,22 +3441,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3560,22 +3560,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3679,22 +3679,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3798,17 +3798,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3917,22 +3917,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4036,22 +4036,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4155,22 +4155,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4274,22 +4274,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4393,17 +4393,17 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4512,17 +4512,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4631,22 +4631,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4750,22 +4750,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4869,22 +4869,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4988,22 +4988,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5107,22 +5107,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5226,17 +5226,17 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5345,22 +5345,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5464,22 +5464,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5583,22 +5583,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5702,22 +5702,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5821,17 +5821,17 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5940,22 +5940,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6059,22 +6059,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6178,17 +6178,17 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6297,22 +6297,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6416,22 +6416,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6535,17 +6535,17 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6654,17 +6654,17 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6773,22 +6773,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6892,22 +6892,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7011,22 +7011,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7130,22 +7130,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7249,22 +7249,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7421,24 +7421,24 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7497,12 +7497,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -7540,12 +7540,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7606,22 +7606,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7659,24 +7659,24 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7725,22 +7725,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -7773,27 +7773,31 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -7801,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7825,37 +7829,37 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7888,29 +7892,29 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>68分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>16:01采样：该车到重点站唐陆公路春雅路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数31分钟，约±8分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7920,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7944,12 +7948,12 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
@@ -7959,22 +7963,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8007,29 +8011,29 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>16:01采样：该车到重点站唐陆公路唐镇路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±8分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8039,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8063,12 +8067,12 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
@@ -8078,22 +8082,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -8126,29 +8130,29 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>16:01采样：该车到重点站长岛路台儿庄路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8158,7 +8162,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8182,12 +8186,12 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
@@ -8197,22 +8201,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -8245,29 +8249,29 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数69分钟估算，约±7分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8277,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8301,12 +8305,12 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
@@ -8316,22 +8320,22 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8364,29 +8368,29 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数70分钟估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8396,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8420,12 +8424,12 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
@@ -8435,17 +8439,17 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8483,29 +8487,29 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8515,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8539,12 +8543,12 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
@@ -8564,12 +8568,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -8602,29 +8606,29 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数69分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8634,7 +8638,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8658,12 +8662,12 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
@@ -8673,22 +8677,22 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8696,24 +8700,24 @@
       <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>沪A67983D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
-        </is>
-      </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -8721,27 +8725,31 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8749,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8763,7 +8771,7 @@
       <c r="T70" s="2" t="inlineStr"/>
       <c r="U70" s="2" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="V70" s="2" t="inlineStr">
@@ -8773,37 +8781,37 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8819,7 @@
       <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>沪A13735A</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -8821,7 +8829,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -8836,35 +8844,39 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8878,47 +8890,2867 @@
       <c r="T71" s="2" t="inlineStr"/>
       <c r="U71" s="2" t="inlineStr">
         <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="V71" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W71" s="2" t="inlineStr">
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>75.7</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>100分钟</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A32597D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>18:34</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>69.8</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>18:52</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>97分钟</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>82.7</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>18:52</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>74.8</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>77.2</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>78.6</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>19:14</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>79.3</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>76.8</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>19:29</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>75.4</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：19:21采样，终点ETA 12分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>75.4</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X71" s="2" t="inlineStr">
+      <c r="X84" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y71" s="2" t="inlineStr">
+      <c r="Y84" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z71" s="2" t="inlineStr">
+      <c r="Z84" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB71" s="2" t="inlineStr">
-        <is>
-          <t>80.8</t>
-        </is>
-      </c>
-      <c r="AC71" s="2" t="inlineStr">
-        <is>
-          <t>13/14</t>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>75.7</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A32597D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>69.8</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>77分钟</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：19:31采样，终点ETA 50分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>74.8</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>79.3</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>77.2</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>21:04</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>75.4</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>21:07</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>78.6</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>21:22</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
         </is>
       </c>
     </row>
